--- a/2022 data/excel_outputs/272_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/272_boothwise_data.xlsx
@@ -14,11 +14,86 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="477">
   <si>
     <t>AC 272 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -727,7 +802,7 @@
     <t>P.S. POKHARA M.PART</t>
   </si>
   <si>
-    <t>U.P.S. POKHARA ■</t>
+    <t>PRATHMIK VIDYALYA HAIDERGARH DEHAT</t>
   </si>
   <si>
     <t>U.P.S. POKHARA R 2</t>
@@ -1376,8 +1451,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1393,7 +1476,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1401,12 +1484,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1705,88 +1806,163 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>428</v>
+        <v>453</v>
       </c>
       <c r="D2" t="s">
-        <v>429</v>
+        <v>454</v>
       </c>
       <c r="E2" t="s">
-        <v>430</v>
+        <v>455</v>
       </c>
       <c r="F2" t="s">
-        <v>431</v>
+        <v>456</v>
       </c>
       <c r="G2" t="s">
-        <v>432</v>
+        <v>457</v>
       </c>
       <c r="H2" t="s">
-        <v>433</v>
+        <v>458</v>
       </c>
       <c r="I2" t="s">
-        <v>434</v>
+        <v>459</v>
       </c>
       <c r="J2" t="s">
-        <v>435</v>
+        <v>460</v>
       </c>
       <c r="K2" t="s">
-        <v>436</v>
+        <v>461</v>
       </c>
       <c r="L2" t="s">
-        <v>437</v>
+        <v>462</v>
       </c>
       <c r="M2" t="s">
-        <v>438</v>
+        <v>463</v>
       </c>
       <c r="N2" t="s">
-        <v>439</v>
+        <v>464</v>
       </c>
       <c r="O2" t="s">
-        <v>440</v>
+        <v>465</v>
       </c>
       <c r="P2" t="s">
-        <v>441</v>
+        <v>466</v>
       </c>
       <c r="Q2" t="s">
-        <v>442</v>
+        <v>467</v>
       </c>
       <c r="R2" t="s">
-        <v>443</v>
+        <v>468</v>
       </c>
       <c r="S2" t="s">
-        <v>444</v>
+        <v>469</v>
       </c>
       <c r="T2" t="s">
-        <v>445</v>
+        <v>470</v>
       </c>
       <c r="U2" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="V2" t="s">
-        <v>447</v>
+        <v>472</v>
       </c>
       <c r="W2" t="s">
-        <v>448</v>
+        <v>473</v>
       </c>
       <c r="X2" t="s">
-        <v>449</v>
+        <v>474</v>
       </c>
       <c r="Y2" t="s">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="Z2" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
     </row>
     <row r="3" spans="1:26">
@@ -1794,7 +1970,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>1157</v>
@@ -1874,7 +2050,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C4">
         <v>672</v>
@@ -1954,7 +2130,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C5">
         <v>726</v>
@@ -2034,7 +2210,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>799</v>
@@ -2114,7 +2290,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>450</v>
@@ -2194,7 +2370,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <v>773</v>
@@ -2274,7 +2450,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C9">
         <v>508</v>
@@ -2354,7 +2530,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C10">
         <v>789</v>
@@ -2434,7 +2610,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C11">
         <v>438</v>
@@ -2514,7 +2690,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C12">
         <v>554</v>
@@ -2594,7 +2770,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C13">
         <v>764</v>
@@ -2674,7 +2850,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="C14">
         <v>1056</v>
@@ -2754,7 +2930,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C15">
         <v>934</v>
@@ -2834,7 +3010,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C16">
         <v>516</v>
@@ -2914,7 +3090,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="C17">
         <v>304</v>
@@ -2994,7 +3170,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="C18">
         <v>502</v>
@@ -3074,7 +3250,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C19">
         <v>607</v>
@@ -3154,7 +3330,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C20">
         <v>615</v>
@@ -3234,7 +3410,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="C21">
         <v>531</v>
@@ -3314,7 +3490,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="C22">
         <v>671</v>
@@ -3394,7 +3570,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="C23">
         <v>741</v>
@@ -3474,7 +3650,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C24">
         <v>764</v>
@@ -3554,7 +3730,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C25">
         <v>722</v>
@@ -3634,7 +3810,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C26">
         <v>958</v>
@@ -3714,7 +3890,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="C27">
         <v>880</v>
@@ -3794,7 +3970,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C28">
         <v>806</v>
@@ -3874,7 +4050,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="C29">
         <v>820</v>
@@ -3954,7 +4130,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C30">
         <v>726</v>
@@ -4034,7 +4210,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C31">
         <v>986</v>
@@ -4114,7 +4290,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="C32">
         <v>937</v>
@@ -4194,7 +4370,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C33">
         <v>958</v>
@@ -4274,7 +4450,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C34">
         <v>974</v>
@@ -4354,7 +4530,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="C35">
         <v>756</v>
@@ -4434,7 +4610,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C36">
         <v>966</v>
@@ -4514,7 +4690,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="C37">
         <v>855</v>
@@ -4594,7 +4770,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="C38">
         <v>859</v>
@@ -4674,7 +4850,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C39">
         <v>915</v>
@@ -4754,7 +4930,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="C40">
         <v>508</v>
@@ -4834,7 +5010,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="C41">
         <v>1040</v>
@@ -4914,7 +5090,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="C42">
         <v>749</v>
@@ -4994,7 +5170,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="C43">
         <v>806</v>
@@ -5074,7 +5250,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C44">
         <v>675</v>
@@ -5154,7 +5330,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="C45">
         <v>510</v>
@@ -5234,7 +5410,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C46">
         <v>463</v>
@@ -5314,7 +5490,7 @@
         <v>47</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="C47">
         <v>863</v>
@@ -5394,7 +5570,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C48">
         <v>735</v>
@@ -5474,7 +5650,7 @@
         <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="C49">
         <v>764</v>
@@ -5554,7 +5730,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="C50">
         <v>375</v>
@@ -5634,7 +5810,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="C51">
         <v>671</v>
@@ -5714,7 +5890,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="C52">
         <v>713</v>
@@ -5794,7 +5970,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="C53">
         <v>343</v>
@@ -5874,7 +6050,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="C54">
         <v>607</v>
@@ -5954,7 +6130,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="C55">
         <v>584</v>
@@ -6034,7 +6210,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C56">
         <v>833</v>
@@ -6114,7 +6290,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="C57">
         <v>668</v>
@@ -6194,7 +6370,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="C58">
         <v>986</v>
@@ -6274,7 +6450,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="C59">
         <v>1193</v>
@@ -6354,7 +6530,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="C60">
         <v>693</v>
@@ -6434,7 +6610,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="C61">
         <v>769</v>
@@ -6514,7 +6690,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="C62">
         <v>1108</v>
@@ -6594,7 +6770,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="C63">
         <v>746</v>
@@ -6674,7 +6850,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="C64">
         <v>794</v>
@@ -6754,7 +6930,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="C65">
         <v>1025</v>
@@ -6834,7 +7010,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="C66">
         <v>828</v>
@@ -6914,7 +7090,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="C67">
         <v>1072</v>
@@ -6994,7 +7170,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="C68">
         <v>1130</v>
@@ -7074,7 +7250,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="C69">
         <v>1033</v>
@@ -7154,7 +7330,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="C70">
         <v>1040</v>
@@ -7234,7 +7410,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="C71">
         <v>752</v>
@@ -7314,7 +7490,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="C72">
         <v>743</v>
@@ -7394,7 +7570,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="C73">
         <v>891</v>
@@ -7474,7 +7650,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="C74">
         <v>1010</v>
@@ -7554,7 +7730,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="C75">
         <v>724</v>
@@ -7634,7 +7810,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C76">
         <v>950</v>
@@ -7714,7 +7890,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C77">
         <v>946</v>
@@ -7794,7 +7970,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C78">
         <v>1163</v>
@@ -7874,7 +8050,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C79">
         <v>829</v>
@@ -7954,7 +8130,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="C80">
         <v>1154</v>
@@ -8034,7 +8210,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="C81">
         <v>951</v>
@@ -8114,7 +8290,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="C82">
         <v>987</v>
@@ -8194,7 +8370,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C83">
         <v>672</v>
@@ -8274,7 +8450,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="C84">
         <v>800</v>
@@ -8354,7 +8530,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="C85">
         <v>864</v>
@@ -8434,7 +8610,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="C86">
         <v>789</v>
@@ -8514,7 +8690,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="C87">
         <v>1004</v>
@@ -8594,7 +8770,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="C88">
         <v>1018</v>
@@ -8674,7 +8850,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="C89">
         <v>1016</v>
@@ -8754,7 +8930,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="C90">
         <v>1052</v>
@@ -8834,7 +9010,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="C91">
         <v>484</v>
@@ -8914,7 +9090,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="C92">
         <v>599</v>
@@ -8994,7 +9170,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="C93">
         <v>595</v>
@@ -9074,7 +9250,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="C94">
         <v>409</v>
@@ -9154,7 +9330,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C95">
         <v>769</v>
@@ -9234,7 +9410,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="C96">
         <v>639</v>
@@ -9314,7 +9490,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="C97">
         <v>742</v>
@@ -9394,7 +9570,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="C98">
         <v>953</v>
@@ -9474,7 +9650,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="C99">
         <v>886</v>
@@ -9554,7 +9730,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="C100">
         <v>721</v>
@@ -9634,7 +9810,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="C101">
         <v>620</v>
@@ -9714,7 +9890,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="C102">
         <v>770</v>
@@ -9794,7 +9970,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="C103">
         <v>686</v>
@@ -9874,7 +10050,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="C104">
         <v>728</v>
@@ -9954,7 +10130,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="C105">
         <v>906</v>
@@ -10034,7 +10210,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="C106">
         <v>995</v>
@@ -10114,7 +10290,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="C107">
         <v>931</v>
@@ -10194,7 +10370,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="C108">
         <v>921</v>
@@ -10274,7 +10450,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="C109">
         <v>836</v>
@@ -10354,7 +10530,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="C110">
         <v>782</v>
@@ -10434,7 +10610,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="C111">
         <v>735</v>
@@ -10514,7 +10690,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="C112">
         <v>574</v>
@@ -10594,7 +10770,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="C113">
         <v>645</v>
@@ -10674,7 +10850,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="C114">
         <v>685</v>
@@ -10754,7 +10930,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="C115">
         <v>1098</v>
@@ -10834,7 +11010,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="C116">
         <v>1116</v>
@@ -10914,7 +11090,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="C117">
         <v>1039</v>
@@ -10994,7 +11170,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="C118">
         <v>948</v>
@@ -11074,7 +11250,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="C119">
         <v>880</v>
@@ -11154,7 +11330,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="C120">
         <v>687</v>
@@ -11234,7 +11410,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="C121">
         <v>407</v>
@@ -11314,7 +11490,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C122">
         <v>577</v>
@@ -11394,7 +11570,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="C123">
         <v>984</v>
@@ -11474,7 +11650,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="C124">
         <v>646</v>
@@ -11554,7 +11730,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="C125">
         <v>800</v>
@@ -11634,7 +11810,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="C126">
         <v>474</v>
@@ -11714,7 +11890,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="C127">
         <v>638</v>
@@ -11794,7 +11970,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="C128">
         <v>820</v>
@@ -11874,7 +12050,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="C129">
         <v>680</v>
@@ -11954,7 +12130,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="C130">
         <v>603</v>
@@ -12034,7 +12210,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="C131">
         <v>988</v>
@@ -12114,7 +12290,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="C132">
         <v>631</v>
@@ -12194,7 +12370,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="C133">
         <v>701</v>
@@ -12274,7 +12450,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="C134">
         <v>761</v>
@@ -12354,7 +12530,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="C135">
         <v>692</v>
@@ -12434,7 +12610,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="C136">
         <v>772</v>
@@ -12514,7 +12690,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="C137">
         <v>752</v>
@@ -12594,7 +12770,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="C138">
         <v>761</v>
@@ -12674,7 +12850,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="C139">
         <v>699</v>
@@ -12754,7 +12930,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="C140">
         <v>746</v>
@@ -12834,7 +13010,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="C141">
         <v>791</v>
@@ -12914,7 +13090,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="C142">
         <v>589</v>
@@ -12994,7 +13170,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="C143">
         <v>731</v>
@@ -13074,7 +13250,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="C144">
         <v>746</v>
@@ -13154,7 +13330,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="C145">
         <v>943</v>
@@ -13234,7 +13410,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="C146">
         <v>1022</v>
@@ -13314,7 +13490,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="C147">
         <v>910</v>
@@ -13394,7 +13570,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="C148">
         <v>909</v>
@@ -13474,7 +13650,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="C149">
         <v>405</v>
@@ -13554,7 +13730,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="C150">
         <v>598</v>
@@ -13634,7 +13810,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="C151">
         <v>860</v>
@@ -13714,7 +13890,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="C152">
         <v>890</v>
@@ -13794,7 +13970,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="C153">
         <v>619</v>
@@ -13874,7 +14050,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="C154">
         <v>773</v>
@@ -13954,7 +14130,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="C155">
         <v>640</v>
@@ -14034,7 +14210,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="C156">
         <v>263</v>
@@ -14114,7 +14290,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="C157">
         <v>430</v>
@@ -14194,7 +14370,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="C158">
         <v>778</v>
@@ -14274,7 +14450,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="C159">
         <v>1068</v>
@@ -14354,7 +14530,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="C160">
         <v>1118</v>
@@ -14434,7 +14610,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="C161">
         <v>664</v>
@@ -14514,7 +14690,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="C162">
         <v>887</v>
@@ -14594,7 +14770,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="C163">
         <v>1047</v>
@@ -14674,7 +14850,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="C164">
         <v>612</v>
@@ -14754,7 +14930,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="C165">
         <v>965</v>
@@ -14834,7 +15010,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="C166">
         <v>657</v>
@@ -14914,7 +15090,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="C167">
         <v>576</v>
@@ -14994,7 +15170,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="C168">
         <v>531</v>
@@ -15074,7 +15250,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="C169">
         <v>698</v>
@@ -15154,7 +15330,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="C170">
         <v>1024</v>
@@ -15234,7 +15410,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C171">
         <v>572</v>
@@ -15314,7 +15490,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="C172">
         <v>1006</v>
@@ -15394,7 +15570,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="C173">
         <v>587</v>
@@ -15474,7 +15650,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="C174">
         <v>722</v>
@@ -15554,7 +15730,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="C175">
         <v>693</v>
@@ -15634,7 +15810,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="C176">
         <v>656</v>
@@ -15714,7 +15890,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="C177">
         <v>672</v>
@@ -15794,7 +15970,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="C178">
         <v>1107</v>
@@ -15874,7 +16050,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="C179">
         <v>1127</v>
@@ -15954,7 +16130,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="C180">
         <v>766</v>
@@ -16034,7 +16210,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="C181">
         <v>561</v>
@@ -16114,7 +16290,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="C182">
         <v>1075</v>
@@ -16194,7 +16370,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="C183">
         <v>422</v>
@@ -16274,7 +16450,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="C184">
         <v>702</v>
@@ -16354,7 +16530,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="C185">
         <v>779</v>
@@ -16434,7 +16610,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="C186">
         <v>837</v>
@@ -16514,7 +16690,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="C187">
         <v>510</v>
@@ -16594,7 +16770,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="C188">
         <v>607</v>
@@ -16674,7 +16850,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="C189">
         <v>582</v>
@@ -16754,7 +16930,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="C190">
         <v>823</v>
@@ -16834,7 +17010,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="C191">
         <v>1118</v>
@@ -16914,7 +17090,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="C192">
         <v>424</v>
@@ -16994,7 +17170,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="C193">
         <v>750</v>
@@ -17074,7 +17250,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="C194">
         <v>680</v>
@@ -17154,7 +17330,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="C195">
         <v>653</v>
@@ -17234,7 +17410,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="C196">
         <v>871</v>
@@ -17314,7 +17490,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="C197">
         <v>988</v>
@@ -17394,7 +17570,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="C198">
         <v>1005</v>
@@ -17474,7 +17650,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="C199">
         <v>910</v>
@@ -17554,7 +17730,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="C200">
         <v>1028</v>
@@ -17634,7 +17810,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="C201">
         <v>733</v>
@@ -17714,7 +17890,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="C202">
         <v>604</v>
@@ -17794,7 +17970,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="C203">
         <v>1134</v>
@@ -17874,7 +18050,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="C204">
         <v>715</v>
@@ -17954,7 +18130,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="C205">
         <v>639</v>
@@ -18034,7 +18210,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="C206">
         <v>344</v>
@@ -18114,7 +18290,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="C207">
         <v>729</v>
@@ -18194,7 +18370,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="C208">
         <v>996</v>
@@ -18274,7 +18450,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="C209">
         <v>652</v>
@@ -18354,7 +18530,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="C210">
         <v>823</v>
@@ -18434,7 +18610,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="C211">
         <v>1127</v>
@@ -18514,7 +18690,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="C212">
         <v>739</v>
@@ -18594,7 +18770,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="C213">
         <v>1070</v>
@@ -18674,7 +18850,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="C214">
         <v>881</v>
@@ -18754,7 +18930,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="C215">
         <v>850</v>
@@ -18834,7 +19010,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="C216">
         <v>739</v>
@@ -18914,7 +19090,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="C217">
         <v>933</v>
@@ -18994,7 +19170,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="C218">
         <v>627</v>
@@ -19074,7 +19250,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="C219">
         <v>717</v>
@@ -19154,7 +19330,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>214</v>
+        <v>239</v>
       </c>
       <c r="C220">
         <v>443</v>
@@ -19234,7 +19410,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C221">
         <v>824</v>
@@ -19314,7 +19490,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="C222">
         <v>574</v>
@@ -19394,7 +19570,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="C223">
         <v>602</v>
@@ -19474,7 +19650,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="C224">
         <v>887</v>
@@ -19554,7 +19730,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="C225">
         <v>645</v>
@@ -19634,7 +19810,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="C226">
         <v>628</v>
@@ -19714,7 +19890,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="C227">
         <v>899</v>
@@ -19794,7 +19970,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="C228">
         <v>842</v>
@@ -19874,7 +20050,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="C229">
         <v>717</v>
@@ -19954,7 +20130,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="C230">
         <v>719</v>
@@ -20034,7 +20210,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="C231">
         <v>984</v>
@@ -20114,7 +20290,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="C232">
         <v>673</v>
@@ -20194,7 +20370,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="C233">
         <v>1019</v>
@@ -20274,7 +20450,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>228</v>
+        <v>253</v>
       </c>
       <c r="C234">
         <v>946</v>
@@ -20354,7 +20530,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="C235">
         <v>1095</v>
@@ -20434,7 +20610,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="C236">
         <v>1041</v>
@@ -20514,7 +20690,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="C237">
         <v>541</v>
@@ -20594,7 +20770,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="C238">
         <v>1132</v>
@@ -20674,7 +20850,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="C239">
         <v>501</v>
@@ -20754,7 +20930,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="C240">
         <v>1026</v>
@@ -20834,7 +21010,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="C241">
         <v>923</v>
@@ -20914,7 +21090,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="C242">
         <v>953</v>
@@ -20994,7 +21170,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="C243">
         <v>763</v>
@@ -21074,7 +21250,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="C244">
         <v>898</v>
@@ -21154,7 +21330,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="C245">
         <v>897</v>
@@ -21234,7 +21410,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="C246">
         <v>618</v>
@@ -21314,7 +21490,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="C247">
         <v>571</v>
@@ -21394,7 +21570,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="C248">
         <v>464</v>
@@ -21474,7 +21650,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="C249">
         <v>855</v>
@@ -21554,7 +21730,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>244</v>
+        <v>269</v>
       </c>
       <c r="C250">
         <v>811</v>
@@ -21634,7 +21810,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="C251">
         <v>1005</v>
@@ -21714,7 +21890,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="C252">
         <v>689</v>
@@ -21794,7 +21970,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>247</v>
+        <v>272</v>
       </c>
       <c r="C253">
         <v>653</v>
@@ -21874,7 +22050,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="C254">
         <v>1124</v>
@@ -21954,7 +22130,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="C255">
         <v>476</v>
@@ -22034,7 +22210,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="C256">
         <v>779</v>
@@ -22114,7 +22290,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="C257">
         <v>605</v>
@@ -22194,7 +22370,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="C258">
         <v>1147</v>
@@ -22274,7 +22450,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="C259">
         <v>1140</v>
@@ -22354,7 +22530,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="C260">
         <v>823</v>
@@ -22434,7 +22610,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="C261">
         <v>839</v>
@@ -22514,7 +22690,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>256</v>
+        <v>281</v>
       </c>
       <c r="C262">
         <v>825</v>
@@ -22594,7 +22770,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>257</v>
+        <v>282</v>
       </c>
       <c r="C263">
         <v>724</v>
@@ -22674,7 +22850,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>258</v>
+        <v>283</v>
       </c>
       <c r="C264">
         <v>914</v>
@@ -22754,7 +22930,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="C265">
         <v>603</v>
@@ -22834,7 +23010,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="C266">
         <v>603</v>
@@ -22914,7 +23090,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="C267">
         <v>942</v>
@@ -22994,7 +23170,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="C268">
         <v>546</v>
@@ -23074,7 +23250,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="C269">
         <v>527</v>
@@ -23154,7 +23330,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="C270">
         <v>1040</v>
@@ -23234,7 +23410,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="C271">
         <v>659</v>
@@ -23314,7 +23490,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="C272">
         <v>731</v>
@@ -23394,7 +23570,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="C273">
         <v>828</v>
@@ -23474,7 +23650,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="C274">
         <v>830</v>
@@ -23554,7 +23730,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>269</v>
+        <v>294</v>
       </c>
       <c r="C275">
         <v>833</v>
@@ -23634,7 +23810,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>270</v>
+        <v>295</v>
       </c>
       <c r="C276">
         <v>835</v>
@@ -23714,7 +23890,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="C277">
         <v>993</v>
@@ -23794,7 +23970,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>272</v>
+        <v>297</v>
       </c>
       <c r="C278">
         <v>892</v>
@@ -23874,7 +24050,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="C279">
         <v>916</v>
@@ -23954,7 +24130,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>273</v>
+        <v>298</v>
       </c>
       <c r="C280">
         <v>1048</v>
@@ -24034,7 +24210,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c r="C281">
         <v>771</v>
@@ -24114,7 +24290,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="C282">
         <v>996</v>
@@ -24194,7 +24370,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="C283">
         <v>1109</v>
@@ -24274,7 +24450,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>277</v>
+        <v>302</v>
       </c>
       <c r="C284">
         <v>972</v>
@@ -24354,7 +24530,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>278</v>
+        <v>303</v>
       </c>
       <c r="C285">
         <v>1119</v>
@@ -24434,7 +24610,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>279</v>
+        <v>304</v>
       </c>
       <c r="C286">
         <v>1145</v>
@@ -24514,7 +24690,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="C287">
         <v>666</v>
@@ -24594,7 +24770,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="C288">
         <v>1105</v>
@@ -24674,7 +24850,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>281</v>
+        <v>306</v>
       </c>
       <c r="C289">
         <v>314</v>
@@ -24754,7 +24930,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="C290">
         <v>1059</v>
@@ -24834,7 +25010,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="C291">
         <v>1036</v>
@@ -24914,7 +25090,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="C292">
         <v>630</v>
@@ -24994,7 +25170,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="C293">
         <v>620</v>
@@ -25074,7 +25250,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="C294">
         <v>889</v>
@@ -25154,7 +25330,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="C295">
         <v>358</v>
@@ -25234,7 +25410,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>288</v>
+        <v>313</v>
       </c>
       <c r="C296">
         <v>723</v>
@@ -25314,7 +25490,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>289</v>
+        <v>314</v>
       </c>
       <c r="C297">
         <v>762</v>
@@ -25394,7 +25570,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="C298">
         <v>440</v>
@@ -25474,7 +25650,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>291</v>
+        <v>316</v>
       </c>
       <c r="C299">
         <v>872</v>
@@ -25554,7 +25730,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="C300">
         <v>1031</v>
@@ -25634,7 +25810,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
       <c r="C301">
         <v>608</v>
@@ -25714,7 +25890,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="C302">
         <v>574</v>
@@ -25794,7 +25970,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>295</v>
+        <v>320</v>
       </c>
       <c r="C303">
         <v>1081</v>
@@ -25874,7 +26050,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>296</v>
+        <v>321</v>
       </c>
       <c r="C304">
         <v>634</v>
@@ -25954,7 +26130,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="C305">
         <v>793</v>
@@ -26034,7 +26210,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>298</v>
+        <v>323</v>
       </c>
       <c r="C306">
         <v>689</v>
@@ -26114,7 +26290,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>299</v>
+        <v>324</v>
       </c>
       <c r="C307">
         <v>958</v>
@@ -26194,7 +26370,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="C308">
         <v>571</v>
@@ -26274,7 +26450,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="C309">
         <v>853</v>
@@ -26354,7 +26530,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="C310">
         <v>948</v>
@@ -26434,7 +26610,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="C311">
         <v>1034</v>
@@ -26514,7 +26690,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>304</v>
+        <v>329</v>
       </c>
       <c r="C312">
         <v>1026</v>
@@ -26594,7 +26770,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>305</v>
+        <v>330</v>
       </c>
       <c r="C313">
         <v>1107</v>
@@ -26674,7 +26850,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="C314">
         <v>485</v>
@@ -26754,7 +26930,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>307</v>
+        <v>332</v>
       </c>
       <c r="C315">
         <v>421</v>
@@ -26834,7 +27010,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>308</v>
+        <v>333</v>
       </c>
       <c r="C316">
         <v>630</v>
@@ -26914,7 +27090,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>309</v>
+        <v>334</v>
       </c>
       <c r="C317">
         <v>608</v>
@@ -26994,7 +27170,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="C318">
         <v>653</v>
@@ -27074,7 +27250,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>311</v>
+        <v>336</v>
       </c>
       <c r="C319">
         <v>644</v>
@@ -27154,7 +27330,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="C320">
         <v>977</v>
@@ -27234,7 +27410,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="C321">
         <v>998</v>
@@ -27314,7 +27490,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="C322">
         <v>952</v>
@@ -27394,7 +27570,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="C323">
         <v>885</v>
@@ -27474,7 +27650,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
       <c r="C324">
         <v>1197</v>
@@ -27554,7 +27730,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="C325">
         <v>606</v>
@@ -27634,7 +27810,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="C326">
         <v>633</v>
@@ -27714,7 +27890,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="C327">
         <v>642</v>
@@ -27794,7 +27970,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="C328">
         <v>570</v>
@@ -27874,7 +28050,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="C329">
         <v>935</v>
@@ -27954,7 +28130,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="C330">
         <v>908</v>
@@ -28034,7 +28210,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>323</v>
+        <v>348</v>
       </c>
       <c r="C331">
         <v>840</v>
@@ -28114,7 +28290,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="C332">
         <v>610</v>
@@ -28194,7 +28370,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="C333">
         <v>689</v>
@@ -28274,7 +28450,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="C334">
         <v>685</v>
@@ -28354,7 +28530,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="C335">
         <v>882</v>
@@ -28434,7 +28610,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>328</v>
+        <v>353</v>
       </c>
       <c r="C336">
         <v>887</v>
@@ -28514,7 +28690,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="C337">
         <v>631</v>
@@ -28594,7 +28770,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="C338">
         <v>1083</v>
@@ -28674,7 +28850,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>331</v>
+        <v>356</v>
       </c>
       <c r="C339">
         <v>796</v>
@@ -28754,7 +28930,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>332</v>
+        <v>357</v>
       </c>
       <c r="C340">
         <v>620</v>
@@ -28834,7 +29010,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>333</v>
+        <v>358</v>
       </c>
       <c r="C341">
         <v>663</v>
@@ -28914,7 +29090,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="C342">
         <v>975</v>
@@ -28994,7 +29170,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>335</v>
+        <v>360</v>
       </c>
       <c r="C343">
         <v>786</v>
@@ -29074,7 +29250,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>336</v>
+        <v>361</v>
       </c>
       <c r="C344">
         <v>973</v>
@@ -29154,7 +29330,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>337</v>
+        <v>362</v>
       </c>
       <c r="C345">
         <v>914</v>
@@ -29234,7 +29410,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>338</v>
+        <v>363</v>
       </c>
       <c r="C346">
         <v>809</v>
@@ -29314,7 +29490,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>339</v>
+        <v>364</v>
       </c>
       <c r="C347">
         <v>1101</v>
@@ -29394,7 +29570,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>340</v>
+        <v>365</v>
       </c>
       <c r="C348">
         <v>638</v>
@@ -29474,7 +29650,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>341</v>
+        <v>366</v>
       </c>
       <c r="C349">
         <v>714</v>
@@ -29554,7 +29730,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="C350">
         <v>504</v>
@@ -29634,7 +29810,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>343</v>
+        <v>368</v>
       </c>
       <c r="C351">
         <v>1101</v>
@@ -29714,7 +29890,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>344</v>
+        <v>369</v>
       </c>
       <c r="C352">
         <v>1032</v>
@@ -29794,7 +29970,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>345</v>
+        <v>370</v>
       </c>
       <c r="C353">
         <v>1056</v>
@@ -29874,7 +30050,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>346</v>
+        <v>371</v>
       </c>
       <c r="C354">
         <v>1084</v>
@@ -29954,7 +30130,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="C355">
         <v>935</v>
@@ -30034,7 +30210,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>348</v>
+        <v>373</v>
       </c>
       <c r="C356">
         <v>937</v>
@@ -30114,7 +30290,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>349</v>
+        <v>374</v>
       </c>
       <c r="C357">
         <v>916</v>
@@ -30194,7 +30370,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="C358">
         <v>957</v>
@@ -30274,7 +30450,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>351</v>
+        <v>376</v>
       </c>
       <c r="C359">
         <v>895</v>
@@ -30354,7 +30530,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="C360">
         <v>698</v>
@@ -30434,7 +30610,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="C361">
         <v>964</v>
@@ -30514,7 +30690,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>354</v>
+        <v>379</v>
       </c>
       <c r="C362">
         <v>670</v>
@@ -30594,7 +30770,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>355</v>
+        <v>380</v>
       </c>
       <c r="C363">
         <v>636</v>
@@ -30674,7 +30850,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
       <c r="C364">
         <v>574</v>
@@ -30754,7 +30930,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>357</v>
+        <v>382</v>
       </c>
       <c r="C365">
         <v>823</v>
@@ -30834,7 +31010,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>358</v>
+        <v>383</v>
       </c>
       <c r="C366">
         <v>784</v>
@@ -30914,7 +31090,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="C367">
         <v>743</v>
@@ -30994,7 +31170,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>360</v>
+        <v>385</v>
       </c>
       <c r="C368">
         <v>640</v>
@@ -31074,7 +31250,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>361</v>
+        <v>386</v>
       </c>
       <c r="C369">
         <v>833</v>
@@ -31154,7 +31330,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>362</v>
+        <v>387</v>
       </c>
       <c r="C370">
         <v>660</v>
@@ -31234,7 +31410,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>363</v>
+        <v>388</v>
       </c>
       <c r="C371">
         <v>650</v>
@@ -31314,7 +31490,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>364</v>
+        <v>389</v>
       </c>
       <c r="C372">
         <v>1172</v>
@@ -31394,7 +31570,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>365</v>
+        <v>390</v>
       </c>
       <c r="C373">
         <v>723</v>
@@ -31474,7 +31650,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="C374">
         <v>720</v>
@@ -31554,7 +31730,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>367</v>
+        <v>392</v>
       </c>
       <c r="C375">
         <v>514</v>
@@ -31634,7 +31810,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>368</v>
+        <v>393</v>
       </c>
       <c r="C376">
         <v>791</v>
@@ -31714,7 +31890,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>369</v>
+        <v>394</v>
       </c>
       <c r="C377">
         <v>791</v>
@@ -31794,7 +31970,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="C378">
         <v>788</v>
@@ -31874,7 +32050,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="C379">
         <v>799</v>
@@ -31954,7 +32130,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>372</v>
+        <v>397</v>
       </c>
       <c r="C380">
         <v>967</v>
@@ -32034,7 +32210,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>373</v>
+        <v>398</v>
       </c>
       <c r="C381">
         <v>1002</v>
@@ -32114,7 +32290,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="C382">
         <v>788</v>
@@ -32194,7 +32370,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="C383">
         <v>882</v>
@@ -32274,7 +32450,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>376</v>
+        <v>401</v>
       </c>
       <c r="C384">
         <v>934</v>
@@ -32354,7 +32530,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="C385">
         <v>909</v>
@@ -32434,7 +32610,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="C386">
         <v>1111</v>
@@ -32514,7 +32690,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>379</v>
+        <v>404</v>
       </c>
       <c r="C387">
         <v>897</v>
@@ -32594,7 +32770,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="C388">
         <v>1087</v>
@@ -32674,7 +32850,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>381</v>
+        <v>406</v>
       </c>
       <c r="C389">
         <v>931</v>
@@ -32754,7 +32930,7 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>382</v>
+        <v>407</v>
       </c>
       <c r="C390">
         <v>912</v>
@@ -32834,7 +33010,7 @@
         <v>388</v>
       </c>
       <c r="B391" t="s">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="C391">
         <v>962</v>
@@ -32914,7 +33090,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>384</v>
+        <v>409</v>
       </c>
       <c r="C392">
         <v>873</v>
@@ -32994,7 +33170,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>385</v>
+        <v>410</v>
       </c>
       <c r="C393">
         <v>699</v>
@@ -33074,7 +33250,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>386</v>
+        <v>411</v>
       </c>
       <c r="C394">
         <v>660</v>
@@ -33154,7 +33330,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>387</v>
+        <v>412</v>
       </c>
       <c r="C395">
         <v>844</v>
@@ -33234,7 +33410,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>388</v>
+        <v>413</v>
       </c>
       <c r="C396">
         <v>730</v>
@@ -33314,7 +33490,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>389</v>
+        <v>414</v>
       </c>
       <c r="C397">
         <v>891</v>
@@ -33394,7 +33570,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="C398">
         <v>1072</v>
@@ -33474,7 +33650,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>391</v>
+        <v>416</v>
       </c>
       <c r="C399">
         <v>926</v>
@@ -33554,7 +33730,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="C400">
         <v>942</v>
@@ -33634,7 +33810,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>393</v>
+        <v>418</v>
       </c>
       <c r="C401">
         <v>1189</v>
@@ -33714,7 +33890,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>394</v>
+        <v>419</v>
       </c>
       <c r="C402">
         <v>1088</v>
@@ -33794,7 +33970,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="C403">
         <v>1112</v>
@@ -33874,7 +34050,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="C404">
         <v>1181</v>
@@ -33954,7 +34130,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>396</v>
+        <v>421</v>
       </c>
       <c r="C405">
         <v>950</v>
@@ -34034,7 +34210,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="C406">
         <v>1082</v>
@@ -34114,7 +34290,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>398</v>
+        <v>423</v>
       </c>
       <c r="C407">
         <v>995</v>
@@ -34194,7 +34370,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="C408">
         <v>1104</v>
@@ -34274,7 +34450,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="C409">
         <v>1133</v>
@@ -34354,7 +34530,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>401</v>
+        <v>426</v>
       </c>
       <c r="C410">
         <v>1093</v>
@@ -34434,7 +34610,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="C411">
         <v>695</v>
@@ -34514,7 +34690,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>403</v>
+        <v>428</v>
       </c>
       <c r="C412">
         <v>1164</v>
@@ -34594,7 +34770,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>404</v>
+        <v>429</v>
       </c>
       <c r="C413">
         <v>470</v>
@@ -34674,7 +34850,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>405</v>
+        <v>430</v>
       </c>
       <c r="C414">
         <v>1113</v>
@@ -34754,7 +34930,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>406</v>
+        <v>431</v>
       </c>
       <c r="C415">
         <v>488</v>
@@ -34834,7 +35010,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>407</v>
+        <v>432</v>
       </c>
       <c r="C416">
         <v>1015</v>
@@ -34914,7 +35090,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>408</v>
+        <v>433</v>
       </c>
       <c r="C417">
         <v>723</v>
@@ -34994,7 +35170,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>409</v>
+        <v>434</v>
       </c>
       <c r="C418">
         <v>944</v>
@@ -35074,7 +35250,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="C419">
         <v>927</v>
@@ -35154,7 +35330,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="C420">
         <v>1026</v>
@@ -35234,7 +35410,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>412</v>
+        <v>437</v>
       </c>
       <c r="C421">
         <v>618</v>
@@ -35314,7 +35490,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>413</v>
+        <v>438</v>
       </c>
       <c r="C422">
         <v>817</v>
@@ -35394,7 +35570,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>414</v>
+        <v>439</v>
       </c>
       <c r="C423">
         <v>834</v>
@@ -35474,7 +35650,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="C424">
         <v>493</v>
@@ -35554,7 +35730,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>416</v>
+        <v>441</v>
       </c>
       <c r="C425">
         <v>1139</v>
@@ -35634,7 +35810,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>417</v>
+        <v>442</v>
       </c>
       <c r="C426">
         <v>1148</v>
@@ -35714,7 +35890,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>418</v>
+        <v>443</v>
       </c>
       <c r="C427">
         <v>572</v>
@@ -35794,7 +35970,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>419</v>
+        <v>444</v>
       </c>
       <c r="C428">
         <v>616</v>
@@ -35874,7 +36050,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>420</v>
+        <v>445</v>
       </c>
       <c r="C429">
         <v>786</v>
@@ -35954,7 +36130,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>421</v>
+        <v>446</v>
       </c>
       <c r="C430">
         <v>1028</v>
@@ -36034,7 +36210,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>422</v>
+        <v>447</v>
       </c>
       <c r="C431">
         <v>646</v>
@@ -36114,7 +36290,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>423</v>
+        <v>448</v>
       </c>
       <c r="C432">
         <v>638</v>
@@ -36194,7 +36370,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="C433">
         <v>1075</v>
@@ -36274,7 +36450,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="C434">
         <v>624</v>
@@ -36354,7 +36530,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>426</v>
+        <v>451</v>
       </c>
       <c r="C435">
         <v>637</v>
@@ -36434,7 +36610,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>427</v>
+        <v>452</v>
       </c>
       <c r="C436">
         <v>1165</v>
